--- a/DateBase/orders/Dang Nguyen48_2026-8-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-8-11.xlsx
@@ -686,6 +686,9 @@
       <c r="C31" t="str">
         <v>314_松虫草花边黑_scabiosa_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -744,7 +747,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0106106108328761267105513105151510105301510150</v>
+        <v>0106106108328761267105513105151510105301510155</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-8-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-8-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -690,9 +690,20 @@
         <v>5</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>5</v>
+      </c>
+      <c r="C32" t="str">
+        <v>845_干花紫罗兰_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L32"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -747,7 +758,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0106106108328761267105513105151510105301510155</v>
+        <v>010610610832876126710551310515151010530151015530</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-8-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-8-11.xlsx
@@ -760,6 +760,9 @@
       <c r="G2" t="str">
         <v>010610610832876126710551310515151010530151015530</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
